--- a/iter-v1.0.1-第二期/测试用例.xlsx
+++ b/iter-v1.0.1-第二期/测试用例.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cjsj_release\snooker_master_app\iter-v1.0.1-第二期\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\work\cn_app_plus\iter-v1.0.1-第二期\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12900"/>
+    <workbookView windowWidth="28800" windowHeight="12780"/>
   </bookViews>
   <sheets>
     <sheet name="安卓" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="冒烟测试" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">安卓!$A$1:$O$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">安卓!$A$1:$O$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2796" uniqueCount="924">
   <si>
     <t>用例编号</t>
   </si>
@@ -1896,18 +1896,23 @@
     <t>推送到达延迟</t>
   </si>
   <si>
-    <t>通知从事件触发到推送到达的时间</t>
+    <t>推送到达验证-通知最终可达</t>
   </si>
   <si>
     <t>用户已授权通知，App在后台</t>
   </si>
   <si>
     <t>1.触发比赛结束事件
-2.记录从比赛结束到通知出现在通知栏的时间</t>
-  </si>
-  <si>
-    <t>1.推送到达时间≤30s
-2.App在后台和杀掉进程两种情况均能收到</t>
+2.App在后台时记录是否收到通知
+3.App杀掉进程后重复测试</t>
+  </si>
+  <si>
+    <t>1.App在后台时能收到推送通知
+2.App杀掉进程后也能收到推送通知
+3.通知内容和跳转正常</t>
+  </si>
+  <si>
+    <t>推送到达时间依赖极光推送第三方平台，服务端无法控制具体时效</t>
   </si>
   <si>
     <t>斯诺克大师V1.0.1-0080</t>
@@ -2041,6 +2046,340 @@
 2.通知标题和内容正确
 3.杀掉进程后仍能收到制作成功推送
 4.点击通知可正确跳转到目标页面</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0086</t>
+  </si>
+  <si>
+    <t>推送时效性-离线消息补推</t>
+  </si>
+  <si>
+    <t>离线消息补推-断网重连后收到推送</t>
+  </si>
+  <si>
+    <t>用户已授权通知权限，此前已收到过比赛结果推送</t>
+  </si>
+  <si>
+    <t>1.断开设备网络（关闭WiFi和蜂窝数据）
+2.触发比赛结束事件（服务端推送）
+3.恢复设备网络连接
+4.查看通知栏</t>
+  </si>
+  <si>
+    <t>1.断网期间不显示通知
+2.网络恢复后收到离线期间的推送通知
+3.通知标题：比赛结果通知
+4.点击通知正确跳转到场详情页</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0087</t>
+  </si>
+  <si>
+    <t>推送时效性-弱网环境推送</t>
+  </si>
+  <si>
+    <t>弱网环境下推送到达</t>
+  </si>
+  <si>
+    <t>设备处于2G弱网环境（网络限速128kbps）</t>
+  </si>
+  <si>
+    <t>1.在弱网环境下触发比赛结束事件
+2.观察通知栏
+3.等待网络恢复正常后再次触发</t>
+  </si>
+  <si>
+    <t>1.弱网期间推送可能延迟
+2.网络恢复后推送到达
+3.通知内容和跳转正常</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0088</t>
+  </si>
+  <si>
+    <t>推送时效性-飞行模式推送补推</t>
+  </si>
+  <si>
+    <t>飞行模式关闭后收到补推</t>
+  </si>
+  <si>
+    <t>用户已授权通知权限</t>
+  </si>
+  <si>
+    <t>1.开启设备飞行模式
+2.触发比赛结束事件
+3.关闭飞行模式
+4.查看通知栏</t>
+  </si>
+  <si>
+    <t>1.飞行模式期间无通知
+2.关闭飞行模式后收到推送通知
+3.通知内容和跳转正常</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0089</t>
+  </si>
+  <si>
+    <t>推送时效性-推送去重</t>
+  </si>
+  <si>
+    <t>同一事件不重复推送多条通知</t>
+  </si>
+  <si>
+    <t>用户已授权通知权限，App在后台</t>
+  </si>
+  <si>
+    <t>1.一场比赛结束后触发推送
+2.等待服务端可能多次推送
+3.查看通知栏</t>
+  </si>
+  <si>
+    <t>1.只收到1条比赛结果通知
+2.不出现重复通知</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0090</t>
+  </si>
+  <si>
+    <t>视频制作通知-单杆视频内容验证</t>
+  </si>
+  <si>
+    <t>单杆视频制作成功通知内容正确且跳转横屏播放</t>
+  </si>
+  <si>
+    <t>用户已授权通知权限，有一个单杆视频正在制作</t>
+  </si>
+  <si>
+    <t>1.单杆视频制作完成
+2.查看通知栏
+3.点击通知</t>
+  </si>
+  <si>
+    <t>1.收到推送通知
+2.标题：视频制作成功
+3.内容：单杆XX分视频已制作完成，点击查看详情
+4.跳转到我的视频页面并横屏播放</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0091</t>
+  </si>
+  <si>
+    <t>视频制作通知-集锦内容验证</t>
+  </si>
+  <si>
+    <t>精彩集锦制作完成通知内容正确且跳转正确</t>
+  </si>
+  <si>
+    <t>用户已授权通知权限，有精彩集锦正在制作</t>
+  </si>
+  <si>
+    <t>1.精彩集锦制作完成
+2.查看通知栏
+3.点击通知</t>
+  </si>
+  <si>
+    <t>1.收到推送通知
+2.标题：视频制作成功
+3.内容：精彩集锦已制作完成，点击查看详情
+4.跳转到我的视频页面并横屏播放</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0092</t>
+  </si>
+  <si>
+    <t>视频制作通知-局视频内容验证</t>
+  </si>
+  <si>
+    <t>局视频制作完成通知内容正确且跳转正确</t>
+  </si>
+  <si>
+    <t>用户已授权通知权限，有局视频正在制作</t>
+  </si>
+  <si>
+    <t>1.局视频制作完成
+2.查看通知栏
+3.点击通知</t>
+  </si>
+  <si>
+    <t>1.收到推送通知
+2.标题：视频制作成功
+3.内容：局视频已制作完成，点击查看详情
+4.跳转到我的视频页面并横屏播放</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0093</t>
+  </si>
+  <si>
+    <t>推送时效性-弱网推送补推</t>
+  </si>
+  <si>
+    <t>弱网（2G）环境断网后恢复收到补推</t>
+  </si>
+  <si>
+    <t>设备处于2G弱网环境</t>
+  </si>
+  <si>
+    <t>1.断开网络连接
+2.触发推送事件
+3.恢复网络连接
+4.查看通知栏</t>
+  </si>
+  <si>
+    <t>1.断网期间不显示通知
+2.网络恢复后收到补推
+3.通知内容和跳转正常</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0094</t>
+  </si>
+  <si>
+    <t>多设备推送</t>
+  </si>
+  <si>
+    <t>多设备同时登录时推送同时到达所有设备</t>
+  </si>
+  <si>
+    <t>同一账号在两台安卓设备上同时登录，均已授权通知</t>
+  </si>
+  <si>
+    <t>1.在设备A上触发比赛结束事件
+2.查看设备A通知栏
+3.查看设备B通知栏</t>
+  </si>
+  <si>
+    <t>1.设备A收到推送通知
+2.设备B也收到推送通知
+3.两台设备通知内容一致</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0095</t>
+  </si>
+  <si>
+    <t>通知权限关闭后的引导处理</t>
+  </si>
+  <si>
+    <t>用户关闭通知权限后返回App引导重新开启</t>
+  </si>
+  <si>
+    <t>用户已在系统设置中关闭App通知权限</t>
+  </si>
+  <si>
+    <t>1.在系统设置中关闭App通知权限
+2.返回App
+3.查看App内是否有引导提示</t>
+  </si>
+  <si>
+    <t>1.App检测到通知权限已关闭
+2.App内弹出引导提示引导用户重新开启通知权限</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0096</t>
+  </si>
+  <si>
+    <t>海外App不支持推送</t>
+  </si>
+  <si>
+    <t>海外版App无推送功能</t>
+  </si>
+  <si>
+    <t>安装海外版App</t>
+  </si>
+  <si>
+    <t>1.检查海外版App是否集成极光推送SDK
+2.触发相关事件
+3.查看是否有推送</t>
+  </si>
+  <si>
+    <t>1.海外版App不集成极光推送SDK
+2.不收到任何推送通知</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0097</t>
+  </si>
+  <si>
+    <t>华为旧版鸿蒙(HarmonyOS 4.3及以前)设备</t>
+  </si>
+  <si>
+    <t>1.安装App并授权通知
+2.触发推送事件
+3.杀掉进程后再次触发</t>
+  </si>
+  <si>
+    <t>1.鸿蒙系统正常接收推送
+2.杀掉进程后仍能收到
+3.通知内容和跳转正确</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0098</t>
+  </si>
+  <si>
+    <t>各厂商推送通道通知样式一致</t>
+  </si>
+  <si>
+    <t>华为/小米/OPPO/vivo设备各一台</t>
+  </si>
+  <si>
+    <t>1.在各厂商设备上触发通知
+2.对比通知栏展示样式</t>
+  </si>
+  <si>
+    <t>1.各厂商通知标题、内容、图标一致
+2.通知样式符合UI设计稿</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0099</t>
+  </si>
+  <si>
+    <t>从App内可跳转至系统通知设置页面</t>
+  </si>
+  <si>
+    <t>App已安装，已授权通知权限</t>
+  </si>
+  <si>
+    <t>1.在App内找到通知设置入口
+2.点击跳转</t>
+  </si>
+  <si>
+    <t>1.成功跳转至系统通知设置页面
+2.在设置页可重新开启/关闭通知</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0100</t>
+  </si>
+  <si>
+    <t>拒绝通知权限后事件发生时不收到推送</t>
+  </si>
+  <si>
+    <t>用户首次安装App时拒绝通知权限</t>
+  </si>
+  <si>
+    <t>1.触发比赛结束事件
+2.触发视频制作完成事件
+3.查看通知栏</t>
+  </si>
+  <si>
+    <t>1.通知栏无任何推送通知
+2.App内功能使用不受影响</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0101</t>
+  </si>
+  <si>
+    <t>杀进程后仍能收到推送</t>
+  </si>
+  <si>
+    <t>杀掉App进程后仍能通过厂商通道收到推送</t>
+  </si>
+  <si>
+    <t>1.打开App后杀掉进程（从最近任务清除）
+2.触发比赛结束事件
+3.查看通知栏
+4.点击通知</t>
+  </si>
+  <si>
+    <t>1.杀掉进程后仍能收到推送
+2.通知标题和内容正确
+3.点击通知正确跳转到目标页面</t>
   </si>
   <si>
     <t>IAP支付解锁视频成功</t>
@@ -2885,6 +3224,218 @@
   <si>
     <t>1.微信：【已发送】+返回/留在微信按钮
 2.抖音：【已发布】+返回/留在抖音按钮</t>
+  </si>
+  <si>
+    <t>首次安装App并打开时询问通知权限</t>
+  </si>
+  <si>
+    <t>1.首次安装并打开App
+2.查看是否弹出通知权限请求
+3.选择【始终允许】</t>
+  </si>
+  <si>
+    <t>1.系统弹出通知权限请求弹窗
+2.允许后App可接收推送通知</t>
+  </si>
+  <si>
+    <t>用户已授权通知权限，App不在前台</t>
+  </si>
+  <si>
+    <t>1.进行一场完整比赛
+2.比赛结束后App退到后台
+3.查看通知栏
+4.点击通知</t>
+  </si>
+  <si>
+    <t>1.收到推送通知
+2.标题：比赛结果通知
+3.内容：比赛结束，点击查看详情
+4.跳转到场详情页-视频回放tab</t>
+  </si>
+  <si>
+    <t>1.解锁视频等待制作完成
+2.App退到后台
+3.等待制作完成推送
+4.查看通知栏</t>
+  </si>
+  <si>
+    <t>1.收到推送通知
+2.标题：视频制作成功
+3.内容根据视频类型显示
+4.点击跳转到我的视频页面横屏播放</t>
+  </si>
+  <si>
+    <t>1.模拟视频制作失败
+2.App退到后台
+3.查看通知栏
+4.点击通知</t>
+  </si>
+  <si>
+    <t>1.收到推送通知
+2.标题：视频制作失败
+3.内容根据视频类型显示
+4.点击跳转到我的视频-失效视频页面</t>
+  </si>
+  <si>
+    <t>1.保持App在前台
+2.触发比赛结束事件
+3.查看通知栏</t>
+  </si>
+  <si>
+    <t>1.App在前台时不弹出通知
+2.退到后台后同事件触发时正常推送</t>
+  </si>
+  <si>
+    <t>APNs推送通道</t>
+  </si>
+  <si>
+    <t>iOS设备通过APNs通道正常接收推送</t>
+  </si>
+  <si>
+    <t>iOS 15+设备</t>
+  </si>
+  <si>
+    <t>1.在iOS设备上安装App
+2.授权通知权限
+3.App退到后台（可杀掉进程）
+4.触发推送事件</t>
+  </si>
+  <si>
+    <t>1.通过APNs通道收到通知
+2.通知内容正确
+3.点击通知正确跳转</t>
+  </si>
+  <si>
+    <t>1.断开设备网络
+2.触发比赛结束事件
+3.恢复网络连接
+4.查看通知栏</t>
+  </si>
+  <si>
+    <t>1.断网期间不显示通知
+2.网络恢复后收到推送通知
+3.通知内容和跳转正常</t>
+  </si>
+  <si>
+    <t>1.弱网环境下触发比赛结束事件
+2.观察通知栏
+3.网络恢复后再次触发</t>
+  </si>
+  <si>
+    <t>1.开启飞行模式
+2.触发比赛结束事件
+3.关闭飞行模式
+4.查看通知栏</t>
+  </si>
+  <si>
+    <t>1.飞行模式期间无通知
+2.关闭后收到推送
+3.通知内容和跳转正常</t>
+  </si>
+  <si>
+    <t>1.一场比赛结束后触发推送
+2.等待
+3.查看通知栏</t>
+  </si>
+  <si>
+    <t>用户已授权通知权限，有单杆视频正在制作</t>
+  </si>
+  <si>
+    <t>1.收到推送通知
+2.标题：视频制作成功
+3.内容：单杆XX分视频已制作完成，点击查看详情
+4.跳转到我的视频并横屏播放</t>
+  </si>
+  <si>
+    <t>1.收到推送通知
+2.标题：视频制作成功
+3.内容：精彩集锦已制作完成，点击查看详情
+4.跳转到我的视频并横屏播放</t>
+  </si>
+  <si>
+    <t>1.收到推送通知
+2.标题：视频制作成功
+3.内容：局视频已制作完成，点击查看详情
+4.跳转到我的视频并横屏播放</t>
+  </si>
+  <si>
+    <t>同一账号在两台iOS设备上同时登录</t>
+  </si>
+  <si>
+    <t>iOS专注模式推送行为</t>
+  </si>
+  <si>
+    <t>iOS专注模式下推送通知行为符合系统预期</t>
+  </si>
+  <si>
+    <t>iOS设备，用户已授权通知权限</t>
+  </si>
+  <si>
+    <t>1.在iOS设备开启专注模式（如工作/睡眠）
+2.触发比赛结束事件
+3.查看通知表现</t>
+  </si>
+  <si>
+    <t>1.推送通知可能被系统静默
+2.通知仍在通知中心可查看
+3.符合iOS系统专注模式行为规范</t>
+  </si>
+  <si>
+    <t>iOS低电量模式推送</t>
+  </si>
+  <si>
+    <t>iOS低电量模式下推送接收正常</t>
+  </si>
+  <si>
+    <t>iOS设备开启低电量模式</t>
+  </si>
+  <si>
+    <t>1.开启低电量模式
+2.App退到后台
+3.触发推送事件
+4.查看通知栏</t>
+  </si>
+  <si>
+    <t>1.低电量模式下仍能收到推送
+2.通知内容和跳转正常</t>
+  </si>
+  <si>
+    <t>1.检查海外版App推送功能
+2.触发相关事件</t>
+  </si>
+  <si>
+    <t>1.海外版App不收到推送通知</t>
+  </si>
+  <si>
+    <t>APNs推送通知样式符合UI设计稿</t>
+  </si>
+  <si>
+    <t>iOS设备</t>
+  </si>
+  <si>
+    <t>1.触发各类通知
+2.查看通知栏样式</t>
+  </si>
+  <si>
+    <t>1.通知标题、内容、图标符合UI设计稿
+2.与其他平台通知风格一致</t>
+  </si>
+  <si>
+    <t>App已安装</t>
+  </si>
+  <si>
+    <t>杀掉App进程后仍能通过APNs收到推送</t>
+  </si>
+  <si>
+    <t>1.打开App后杀掉进程
+2.触发比赛结束事件
+3.查看通知栏
+4.点击通知</t>
+  </si>
+  <si>
+    <t>1.杀掉进程后仍能收到推送
+2.通知标题和内容正确
+3.点击通知正确跳转</t>
   </si>
   <si>
     <t>SM-001</t>
@@ -3479,7 +4030,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -3491,6 +4042,30 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -3624,7 +4199,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -3636,34 +4211,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
@@ -3748,7 +4323,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3760,12 +4335,17 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3776,6 +4356,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4223,7 +4806,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T90"/>
+  <dimension ref="A1:U106"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4309,25 +4892,25 @@
       <c r="A2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
     </row>
     <row r="3" ht="90" customHeight="1" spans="1:20">
       <c r="A3" s="2" t="s">
@@ -4360,14 +4943,14 @@
       <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="8"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="11"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-      <c r="O3" s="8"/>
+      <c r="O3" s="11"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
-      <c r="R3" s="8"/>
+      <c r="R3" s="11"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
     </row>
@@ -4402,14 +4985,14 @@
       <c r="J4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="7"/>
-      <c r="L4" s="8"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="11"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
-      <c r="O4" s="8"/>
+      <c r="O4" s="11"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
-      <c r="R4" s="8"/>
+      <c r="R4" s="11"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
     </row>
@@ -4444,14 +5027,14 @@
       <c r="J5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="8"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="11"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
-      <c r="O5" s="8"/>
+      <c r="O5" s="11"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-      <c r="R5" s="8"/>
+      <c r="R5" s="11"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
     </row>
@@ -4486,14 +5069,14 @@
       <c r="J6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="8"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="11"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
-      <c r="O6" s="8"/>
+      <c r="O6" s="11"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-      <c r="R6" s="8"/>
+      <c r="R6" s="11"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
     </row>
@@ -4529,13 +5112,13 @@
         <v>37</v>
       </c>
       <c r="K7" s="2"/>
-      <c r="L7" s="8"/>
+      <c r="L7" s="11"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="8"/>
+      <c r="O7" s="11"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
-      <c r="R7" s="8"/>
+      <c r="R7" s="11"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
     </row>
@@ -4571,13 +5154,13 @@
         <v>37</v>
       </c>
       <c r="K8" s="2"/>
-      <c r="L8" s="8"/>
+      <c r="L8" s="11"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="8"/>
+      <c r="O8" s="11"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
-      <c r="R8" s="8"/>
+      <c r="R8" s="11"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
     </row>
@@ -4613,13 +5196,13 @@
         <v>30</v>
       </c>
       <c r="K9" s="2"/>
-      <c r="L9" s="8"/>
+      <c r="L9" s="11"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="8"/>
+      <c r="O9" s="11"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
-      <c r="R9" s="8"/>
+      <c r="R9" s="11"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
     </row>
@@ -4655,13 +5238,13 @@
         <v>74</v>
       </c>
       <c r="K10" s="2"/>
-      <c r="L10" s="8"/>
+      <c r="L10" s="11"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="8"/>
+      <c r="O10" s="11"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
-      <c r="R10" s="8"/>
+      <c r="R10" s="11"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
     </row>
@@ -4697,13 +5280,13 @@
         <v>37</v>
       </c>
       <c r="K11" s="2"/>
-      <c r="L11" s="8"/>
+      <c r="L11" s="11"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="8"/>
+      <c r="O11" s="11"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
-      <c r="R11" s="8"/>
+      <c r="R11" s="11"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
@@ -4739,13 +5322,13 @@
         <v>37</v>
       </c>
       <c r="K12" s="2"/>
-      <c r="L12" s="8"/>
+      <c r="L12" s="11"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="8"/>
+      <c r="O12" s="11"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
-      <c r="R12" s="8"/>
+      <c r="R12" s="11"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
@@ -4781,13 +5364,13 @@
         <v>74</v>
       </c>
       <c r="K13" s="2"/>
-      <c r="L13" s="8"/>
+      <c r="L13" s="11"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="8"/>
+      <c r="O13" s="11"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-      <c r="R13" s="8"/>
+      <c r="R13" s="11"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
@@ -4823,13 +5406,13 @@
         <v>37</v>
       </c>
       <c r="K14" s="2"/>
-      <c r="L14" s="8"/>
+      <c r="L14" s="11"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
-      <c r="O14" s="8"/>
+      <c r="O14" s="11"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
-      <c r="R14" s="8"/>
+      <c r="R14" s="11"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
@@ -4865,13 +5448,13 @@
         <v>37</v>
       </c>
       <c r="K15" s="2"/>
-      <c r="L15" s="8"/>
+      <c r="L15" s="11"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
-      <c r="O15" s="8"/>
+      <c r="O15" s="11"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
-      <c r="R15" s="8"/>
+      <c r="R15" s="11"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
     </row>
@@ -4907,13 +5490,13 @@
         <v>74</v>
       </c>
       <c r="K16" s="2"/>
-      <c r="L16" s="8"/>
+      <c r="L16" s="11"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
-      <c r="O16" s="8"/>
+      <c r="O16" s="11"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
-      <c r="R16" s="8"/>
+      <c r="R16" s="11"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
     </row>
@@ -4949,261 +5532,261 @@
         <v>74</v>
       </c>
       <c r="K17" s="2"/>
-      <c r="L17" s="8"/>
+      <c r="L17" s="11"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
-      <c r="O17" s="8"/>
+      <c r="O17" s="11"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
-      <c r="R17" s="8"/>
+      <c r="R17" s="11"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
     </row>
     <row r="18" ht="90" customHeight="1" spans="1:20">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K18" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P18" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R18" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S18" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T18" s="9" t="s">
+      <c r="K18" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M18" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q18" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R18" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S18" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T18" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="19" ht="90" customHeight="1" spans="1:20">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="B19" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K19" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q19" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R19" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S19" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T19" s="9" t="s">
+      <c r="K19" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M19" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P19" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q19" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R19" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S19" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T19" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="20" ht="54" customHeight="1" spans="1:20">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="9" t="s">
+      <c r="B20" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T20" s="9" t="s">
+      <c r="K20" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M20" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q20" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R20" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S20" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T20" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="21" ht="108" customHeight="1" spans="1:20">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="9" t="s">
+      <c r="B21" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K21" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q21" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R21" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S21" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T21" s="9" t="s">
+      <c r="K21" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M21" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O21" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P21" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q21" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R21" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S21" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T21" s="12" t="s">
         <v>125</v>
       </c>
     </row>
@@ -6327,25 +6910,25 @@
       <c r="A40" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="6"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="8"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="8"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
     </row>
     <row r="41" ht="54" customHeight="1" spans="1:20">
       <c r="A41" s="2" t="s">
@@ -6379,13 +6962,13 @@
         <v>30</v>
       </c>
       <c r="K41" s="2"/>
-      <c r="L41" s="8"/>
+      <c r="L41" s="11"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
-      <c r="O41" s="8"/>
+      <c r="O41" s="11"/>
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
-      <c r="R41" s="8"/>
+      <c r="R41" s="11"/>
       <c r="S41" s="2"/>
       <c r="T41" s="2"/>
     </row>
@@ -6421,13 +7004,13 @@
         <v>30</v>
       </c>
       <c r="K42" s="2"/>
-      <c r="L42" s="8"/>
+      <c r="L42" s="11"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
-      <c r="O42" s="8"/>
+      <c r="O42" s="11"/>
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
-      <c r="R42" s="8"/>
+      <c r="R42" s="11"/>
       <c r="S42" s="2"/>
       <c r="T42" s="2"/>
     </row>
@@ -6463,13 +7046,13 @@
         <v>30</v>
       </c>
       <c r="K43" s="2"/>
-      <c r="L43" s="8"/>
+      <c r="L43" s="11"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
-      <c r="O43" s="8"/>
+      <c r="O43" s="11"/>
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
-      <c r="R43" s="8"/>
+      <c r="R43" s="11"/>
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
     </row>
@@ -6505,13 +7088,13 @@
         <v>37</v>
       </c>
       <c r="K44" s="2"/>
-      <c r="L44" s="8"/>
+      <c r="L44" s="11"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
-      <c r="O44" s="8"/>
+      <c r="O44" s="11"/>
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
-      <c r="R44" s="8"/>
+      <c r="R44" s="11"/>
       <c r="S44" s="2"/>
       <c r="T44" s="2"/>
     </row>
@@ -6547,13 +7130,13 @@
         <v>37</v>
       </c>
       <c r="K45" s="2"/>
-      <c r="L45" s="8"/>
+      <c r="L45" s="11"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
-      <c r="O45" s="8"/>
+      <c r="O45" s="11"/>
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
-      <c r="R45" s="8"/>
+      <c r="R45" s="11"/>
       <c r="S45" s="2"/>
       <c r="T45" s="2"/>
     </row>
@@ -6589,13 +7172,13 @@
         <v>37</v>
       </c>
       <c r="K46" s="2"/>
-      <c r="L46" s="8"/>
+      <c r="L46" s="11"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
-      <c r="O46" s="8"/>
+      <c r="O46" s="11"/>
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
-      <c r="R46" s="8"/>
+      <c r="R46" s="11"/>
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
     </row>
@@ -6631,13 +7214,13 @@
         <v>37</v>
       </c>
       <c r="K47" s="2"/>
-      <c r="L47" s="8"/>
+      <c r="L47" s="11"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
-      <c r="O47" s="8"/>
+      <c r="O47" s="11"/>
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
-      <c r="R47" s="8"/>
+      <c r="R47" s="11"/>
       <c r="S47" s="2"/>
       <c r="T47" s="2"/>
     </row>
@@ -6673,13 +7256,13 @@
         <v>37</v>
       </c>
       <c r="K48" s="2"/>
-      <c r="L48" s="8"/>
+      <c r="L48" s="11"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="8"/>
+      <c r="O48" s="11"/>
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
-      <c r="R48" s="8"/>
+      <c r="R48" s="11"/>
       <c r="S48" s="2"/>
       <c r="T48" s="2"/>
     </row>
@@ -6715,13 +7298,13 @@
         <v>37</v>
       </c>
       <c r="K49" s="2"/>
-      <c r="L49" s="8"/>
+      <c r="L49" s="11"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-      <c r="O49" s="8"/>
+      <c r="O49" s="11"/>
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
-      <c r="R49" s="8"/>
+      <c r="R49" s="11"/>
       <c r="S49" s="2"/>
       <c r="T49" s="2"/>
     </row>
@@ -6757,13 +7340,13 @@
         <v>37</v>
       </c>
       <c r="K50" s="2"/>
-      <c r="L50" s="8"/>
+      <c r="L50" s="11"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
-      <c r="O50" s="8"/>
+      <c r="O50" s="11"/>
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
-      <c r="R50" s="8"/>
+      <c r="R50" s="11"/>
       <c r="S50" s="2"/>
       <c r="T50" s="2"/>
     </row>
@@ -6799,13 +7382,13 @@
         <v>74</v>
       </c>
       <c r="K51" s="2"/>
-      <c r="L51" s="8"/>
+      <c r="L51" s="11"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="8"/>
+      <c r="O51" s="11"/>
       <c r="P51" s="2"/>
       <c r="Q51" s="2"/>
-      <c r="R51" s="8"/>
+      <c r="R51" s="11"/>
       <c r="S51" s="2"/>
       <c r="T51" s="2"/>
     </row>
@@ -6841,13 +7424,13 @@
         <v>37</v>
       </c>
       <c r="K52" s="2"/>
-      <c r="L52" s="8"/>
+      <c r="L52" s="11"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="8"/>
+      <c r="O52" s="11"/>
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
-      <c r="R52" s="8"/>
+      <c r="R52" s="11"/>
       <c r="S52" s="2"/>
       <c r="T52" s="2"/>
     </row>
@@ -6883,13 +7466,13 @@
         <v>74</v>
       </c>
       <c r="K53" s="2"/>
-      <c r="L53" s="8"/>
+      <c r="L53" s="11"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
-      <c r="O53" s="8"/>
+      <c r="O53" s="11"/>
       <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
-      <c r="R53" s="8"/>
+      <c r="R53" s="11"/>
       <c r="S53" s="2"/>
       <c r="T53" s="2"/>
     </row>
@@ -6925,199 +7508,199 @@
         <v>74</v>
       </c>
       <c r="K54" s="2"/>
-      <c r="L54" s="8"/>
+      <c r="L54" s="11"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
-      <c r="O54" s="8"/>
+      <c r="O54" s="11"/>
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
-      <c r="R54" s="8"/>
+      <c r="R54" s="11"/>
       <c r="S54" s="2"/>
       <c r="T54" s="2"/>
     </row>
     <row r="55" ht="72" customHeight="1" spans="1:20">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C55" s="9" t="s">
+      <c r="B55" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="12" t="s">
         <v>247</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G55" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="H55" s="9" t="s">
+      <c r="H55" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="I55" s="9" t="s">
+      <c r="I55" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="J55" s="9" t="s">
+      <c r="J55" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K55" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L55" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M55" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N55" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O55" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q55" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R55" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S55" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T55" s="9" t="s">
+      <c r="K55" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L55" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M55" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N55" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O55" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P55" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q55" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R55" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S55" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T55" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="56" ht="36" customHeight="1" spans="1:20">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="B56" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C56" s="9" t="s">
+      <c r="B56" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="12" t="s">
         <v>247</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="H56" s="9" t="s">
+      <c r="H56" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="I56" s="9" t="s">
+      <c r="I56" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="J56" s="9" t="s">
+      <c r="J56" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T56" s="9" t="s">
+      <c r="K56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T56" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="57" ht="72" customHeight="1" spans="1:20">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="B57" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C57" s="9" t="s">
+      <c r="B57" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="12" t="s">
         <v>247</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="H57" s="9" t="s">
+      <c r="H57" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="I57" s="9" t="s">
+      <c r="I57" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="J57" s="9" t="s">
+      <c r="J57" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T57" s="9" t="s">
+      <c r="K57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T57" s="12" t="s">
         <v>125</v>
       </c>
     </row>
@@ -7125,25 +7708,25 @@
       <c r="A58" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="6"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="6"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="4"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9"/>
+      <c r="O58" s="8"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="9"/>
+      <c r="R58" s="8"/>
+      <c r="S58" s="9"/>
+      <c r="T58" s="9"/>
     </row>
     <row r="59" ht="36" customHeight="1" spans="1:20">
       <c r="A59" s="2" t="s">
@@ -7177,13 +7760,13 @@
         <v>30</v>
       </c>
       <c r="K59" s="2"/>
-      <c r="L59" s="8"/>
+      <c r="L59" s="11"/>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
-      <c r="O59" s="8"/>
+      <c r="O59" s="11"/>
       <c r="P59" s="2"/>
       <c r="Q59" s="2"/>
-      <c r="R59" s="8"/>
+      <c r="R59" s="11"/>
       <c r="S59" s="2"/>
       <c r="T59" s="2"/>
     </row>
@@ -7219,13 +7802,13 @@
         <v>37</v>
       </c>
       <c r="K60" s="2"/>
-      <c r="L60" s="8"/>
+      <c r="L60" s="11"/>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
-      <c r="O60" s="8"/>
+      <c r="O60" s="11"/>
       <c r="P60" s="2"/>
       <c r="Q60" s="2"/>
-      <c r="R60" s="8"/>
+      <c r="R60" s="11"/>
       <c r="S60" s="2"/>
       <c r="T60" s="2"/>
     </row>
@@ -7261,13 +7844,13 @@
         <v>37</v>
       </c>
       <c r="K61" s="2"/>
-      <c r="L61" s="8"/>
+      <c r="L61" s="11"/>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
-      <c r="O61" s="8"/>
+      <c r="O61" s="11"/>
       <c r="P61" s="2"/>
       <c r="Q61" s="2"/>
-      <c r="R61" s="8"/>
+      <c r="R61" s="11"/>
       <c r="S61" s="2"/>
       <c r="T61" s="2"/>
     </row>
@@ -7303,13 +7886,13 @@
         <v>30</v>
       </c>
       <c r="K62" s="2"/>
-      <c r="L62" s="8"/>
+      <c r="L62" s="11"/>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
-      <c r="O62" s="8"/>
+      <c r="O62" s="11"/>
       <c r="P62" s="2"/>
       <c r="Q62" s="2"/>
-      <c r="R62" s="8"/>
+      <c r="R62" s="11"/>
       <c r="S62" s="2"/>
       <c r="T62" s="2"/>
     </row>
@@ -7345,13 +7928,13 @@
         <v>37</v>
       </c>
       <c r="K63" s="2"/>
-      <c r="L63" s="8"/>
+      <c r="L63" s="11"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
-      <c r="O63" s="8"/>
+      <c r="O63" s="11"/>
       <c r="P63" s="2"/>
       <c r="Q63" s="2"/>
-      <c r="R63" s="8"/>
+      <c r="R63" s="11"/>
       <c r="S63" s="2"/>
       <c r="T63" s="2"/>
     </row>
@@ -7387,13 +7970,13 @@
         <v>37</v>
       </c>
       <c r="K64" s="2"/>
-      <c r="L64" s="8"/>
+      <c r="L64" s="11"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
-      <c r="O64" s="8"/>
+      <c r="O64" s="11"/>
       <c r="P64" s="2"/>
       <c r="Q64" s="2"/>
-      <c r="R64" s="8"/>
+      <c r="R64" s="11"/>
       <c r="S64" s="2"/>
       <c r="T64" s="2"/>
     </row>
@@ -7429,13 +8012,13 @@
         <v>37</v>
       </c>
       <c r="K65" s="2"/>
-      <c r="L65" s="8"/>
+      <c r="L65" s="11"/>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
-      <c r="O65" s="8"/>
+      <c r="O65" s="11"/>
       <c r="P65" s="2"/>
       <c r="Q65" s="2"/>
-      <c r="R65" s="8"/>
+      <c r="R65" s="11"/>
       <c r="S65" s="2"/>
       <c r="T65" s="2"/>
     </row>
@@ -7471,13 +8054,13 @@
         <v>37</v>
       </c>
       <c r="K66" s="2"/>
-      <c r="L66" s="8"/>
+      <c r="L66" s="11"/>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
-      <c r="O66" s="8"/>
+      <c r="O66" s="11"/>
       <c r="P66" s="2"/>
       <c r="Q66" s="2"/>
-      <c r="R66" s="8"/>
+      <c r="R66" s="11"/>
       <c r="S66" s="2"/>
       <c r="T66" s="2"/>
     </row>
@@ -7513,13 +8096,13 @@
         <v>37</v>
       </c>
       <c r="K67" s="2"/>
-      <c r="L67" s="8"/>
+      <c r="L67" s="11"/>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
-      <c r="O67" s="8"/>
+      <c r="O67" s="11"/>
       <c r="P67" s="2"/>
       <c r="Q67" s="2"/>
-      <c r="R67" s="8"/>
+      <c r="R67" s="11"/>
       <c r="S67" s="2"/>
       <c r="T67" s="2"/>
     </row>
@@ -7555,13 +8138,13 @@
         <v>37</v>
       </c>
       <c r="K68" s="2"/>
-      <c r="L68" s="8"/>
+      <c r="L68" s="11"/>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
-      <c r="O68" s="8"/>
+      <c r="O68" s="11"/>
       <c r="P68" s="2"/>
       <c r="Q68" s="2"/>
-      <c r="R68" s="8"/>
+      <c r="R68" s="11"/>
       <c r="S68" s="2"/>
       <c r="T68" s="2"/>
     </row>
@@ -7597,13 +8180,13 @@
         <v>74</v>
       </c>
       <c r="K69" s="2"/>
-      <c r="L69" s="8"/>
+      <c r="L69" s="11"/>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
-      <c r="O69" s="8"/>
+      <c r="O69" s="11"/>
       <c r="P69" s="2"/>
       <c r="Q69" s="2"/>
-      <c r="R69" s="8"/>
+      <c r="R69" s="11"/>
       <c r="S69" s="2"/>
       <c r="T69" s="2"/>
     </row>
@@ -7639,13 +8222,13 @@
         <v>37</v>
       </c>
       <c r="K70" s="2"/>
-      <c r="L70" s="8"/>
+      <c r="L70" s="11"/>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
-      <c r="O70" s="8"/>
+      <c r="O70" s="11"/>
       <c r="P70" s="2"/>
       <c r="Q70" s="2"/>
-      <c r="R70" s="8"/>
+      <c r="R70" s="11"/>
       <c r="S70" s="2"/>
       <c r="T70" s="2"/>
     </row>
@@ -7681,227 +8264,227 @@
         <v>74</v>
       </c>
       <c r="K71" s="2"/>
-      <c r="L71" s="8"/>
+      <c r="L71" s="11"/>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
-      <c r="O71" s="8"/>
+      <c r="O71" s="11"/>
       <c r="P71" s="2"/>
       <c r="Q71" s="2"/>
-      <c r="R71" s="8"/>
+      <c r="R71" s="11"/>
       <c r="S71" s="2"/>
       <c r="T71" s="2"/>
     </row>
     <row r="72" ht="82.5" customHeight="1" spans="1:20">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="B72" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C72" s="9" t="s">
+      <c r="B72" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" s="12" t="s">
         <v>345</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E72" s="9" t="s">
+      <c r="E72" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="F72" s="9" t="s">
+      <c r="F72" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="G72" s="9" t="s">
+      <c r="G72" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="H72" s="9" t="s">
+      <c r="H72" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="I72" s="9" t="s">
+      <c r="I72" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="J72" s="9" t="s">
+      <c r="J72" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K72" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L72" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M72" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N72" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O72" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P72" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q72" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R72" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S72" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T72" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="73" ht="66" spans="1:20">
-      <c r="A73" s="9" t="s">
+      <c r="K72" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L72" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M72" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N72" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O72" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P72" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q72" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R72" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S72" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T72" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="73" ht="66" customHeight="1" spans="1:20">
+      <c r="A73" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="B73" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C73" s="9" t="s">
+      <c r="B73" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="12" t="s">
         <v>345</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E73" s="9" t="s">
+      <c r="E73" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="F73" s="9" t="s">
+      <c r="F73" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="G73" s="9" t="s">
+      <c r="G73" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="H73" s="9" t="s">
+      <c r="H73" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="I73" s="9" t="s">
+      <c r="I73" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="J73" s="9" t="s">
+      <c r="J73" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K73" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L73" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M73" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N73" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q73" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R73" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S73" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T73" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="74" ht="49.5" spans="1:20">
-      <c r="A74" s="9" t="s">
+      <c r="K73" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L73" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M73" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N73" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O73" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P73" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q73" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R73" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S73" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T73" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="74" ht="49.5" customHeight="1" spans="1:20">
+      <c r="A74" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="B74" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C74" s="9" t="s">
+      <c r="B74" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="12" t="s">
         <v>345</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E74" s="9" t="s">
+      <c r="E74" s="12" t="s">
         <v>434</v>
       </c>
-      <c r="F74" s="9" t="s">
+      <c r="F74" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="G74" s="9" t="s">
+      <c r="G74" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="H74" s="9" t="s">
+      <c r="H74" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="I74" s="9" t="s">
+      <c r="I74" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="J74" s="9" t="s">
+      <c r="J74" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K74" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L74" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M74" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N74" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O74" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P74" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q74" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R74" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S74" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T74" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="75" ht="16.5" spans="1:20">
+      <c r="K74" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L74" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M74" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N74" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O74" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P74" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q74" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R74" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S74" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T74" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" customHeight="1" spans="1:20">
       <c r="A75" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="4"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="6"/>
-      <c r="S75" s="4"/>
-      <c r="T75" s="4"/>
-    </row>
-    <row r="76" ht="66" spans="1:20">
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="9"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="9"/>
+      <c r="N75" s="9"/>
+      <c r="O75" s="8"/>
+      <c r="P75" s="9"/>
+      <c r="Q75" s="9"/>
+      <c r="R75" s="8"/>
+      <c r="S75" s="9"/>
+      <c r="T75" s="9"/>
+    </row>
+    <row r="76" ht="66" customHeight="1" spans="1:20">
       <c r="A76" s="2" t="s">
         <v>439</v>
       </c>
@@ -7933,17 +8516,17 @@
         <v>30</v>
       </c>
       <c r="K76" s="2"/>
-      <c r="L76" s="8"/>
+      <c r="L76" s="11"/>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
-      <c r="O76" s="8"/>
+      <c r="O76" s="11"/>
       <c r="P76" s="2"/>
       <c r="Q76" s="2"/>
-      <c r="R76" s="8"/>
+      <c r="R76" s="11"/>
       <c r="S76" s="2"/>
       <c r="T76" s="2"/>
     </row>
-    <row r="77" ht="82.5" spans="1:20">
+    <row r="77" ht="82.5" customHeight="1" spans="1:20">
       <c r="A77" s="2" t="s">
         <v>446</v>
       </c>
@@ -7975,17 +8558,17 @@
         <v>30</v>
       </c>
       <c r="K77" s="2"/>
-      <c r="L77" s="8"/>
+      <c r="L77" s="11"/>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
-      <c r="O77" s="8"/>
+      <c r="O77" s="11"/>
       <c r="P77" s="2"/>
       <c r="Q77" s="2"/>
-      <c r="R77" s="8"/>
+      <c r="R77" s="11"/>
       <c r="S77" s="2"/>
       <c r="T77" s="2"/>
     </row>
-    <row r="78" ht="165" spans="1:20">
+    <row r="78" ht="165" customHeight="1" spans="1:20">
       <c r="A78" s="2" t="s">
         <v>452</v>
       </c>
@@ -8017,17 +8600,17 @@
         <v>30</v>
       </c>
       <c r="K78" s="2"/>
-      <c r="L78" s="8"/>
+      <c r="L78" s="11"/>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
-      <c r="O78" s="8"/>
+      <c r="O78" s="11"/>
       <c r="P78" s="2"/>
       <c r="Q78" s="2"/>
-      <c r="R78" s="8"/>
+      <c r="R78" s="11"/>
       <c r="S78" s="2"/>
       <c r="T78" s="2"/>
     </row>
-    <row r="79" ht="66" spans="1:20">
+    <row r="79" ht="66" customHeight="1" spans="1:20">
       <c r="A79" s="2" t="s">
         <v>458</v>
       </c>
@@ -8059,17 +8642,17 @@
         <v>30</v>
       </c>
       <c r="K79" s="2"/>
-      <c r="L79" s="8"/>
+      <c r="L79" s="11"/>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
-      <c r="O79" s="8"/>
+      <c r="O79" s="11"/>
       <c r="P79" s="2"/>
       <c r="Q79" s="2"/>
-      <c r="R79" s="8"/>
+      <c r="R79" s="11"/>
       <c r="S79" s="2"/>
       <c r="T79" s="2"/>
     </row>
-    <row r="80" ht="66" spans="1:20">
+    <row r="80" ht="66" customHeight="1" spans="1:20">
       <c r="A80" s="2" t="s">
         <v>464</v>
       </c>
@@ -8101,17 +8684,17 @@
         <v>37</v>
       </c>
       <c r="K80" s="2"/>
-      <c r="L80" s="8"/>
+      <c r="L80" s="11"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
-      <c r="O80" s="8"/>
+      <c r="O80" s="11"/>
       <c r="P80" s="2"/>
       <c r="Q80" s="2"/>
-      <c r="R80" s="8"/>
+      <c r="R80" s="11"/>
       <c r="S80" s="2"/>
       <c r="T80" s="2"/>
     </row>
-    <row r="81" ht="66" spans="1:20">
+    <row r="81" ht="66" customHeight="1" spans="1:21">
       <c r="A81" s="2" t="s">
         <v>470</v>
       </c>
@@ -8143,17 +8726,17 @@
         <v>37</v>
       </c>
       <c r="K81" s="2"/>
-      <c r="L81" s="8"/>
+      <c r="L81" s="11"/>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
-      <c r="O81" s="8"/>
+      <c r="O81" s="11"/>
       <c r="P81" s="2"/>
       <c r="Q81" s="2"/>
-      <c r="R81" s="8"/>
+      <c r="R81" s="11"/>
       <c r="S81" s="2"/>
       <c r="T81" s="2"/>
     </row>
-    <row r="82" ht="66" spans="1:20">
+    <row r="82" ht="66" customHeight="1" spans="1:21">
       <c r="A82" s="2" t="s">
         <v>476</v>
       </c>
@@ -8185,17 +8768,17 @@
         <v>37</v>
       </c>
       <c r="K82" s="2"/>
-      <c r="L82" s="8"/>
+      <c r="L82" s="11"/>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
-      <c r="O82" s="8"/>
+      <c r="O82" s="11"/>
       <c r="P82" s="2"/>
       <c r="Q82" s="2"/>
-      <c r="R82" s="8"/>
+      <c r="R82" s="11"/>
       <c r="S82" s="2"/>
       <c r="T82" s="2"/>
     </row>
-    <row r="83" ht="66" spans="1:20">
+    <row r="83" ht="66" customHeight="1" spans="1:21">
       <c r="A83" s="2" t="s">
         <v>482</v>
       </c>
@@ -8227,17 +8810,17 @@
         <v>37</v>
       </c>
       <c r="K83" s="2"/>
-      <c r="L83" s="8"/>
+      <c r="L83" s="11"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
-      <c r="O83" s="8"/>
+      <c r="O83" s="11"/>
       <c r="P83" s="2"/>
       <c r="Q83" s="2"/>
-      <c r="R83" s="8"/>
+      <c r="R83" s="11"/>
       <c r="S83" s="2"/>
       <c r="T83" s="2"/>
     </row>
-    <row r="84" ht="33" spans="1:20">
+    <row r="84" ht="33" customHeight="1" spans="1:21">
       <c r="A84" s="2" t="s">
         <v>488</v>
       </c>
@@ -8269,19 +8852,21 @@
         <v>37</v>
       </c>
       <c r="K84" s="2"/>
-      <c r="L84" s="8"/>
+      <c r="L84" s="11"/>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
-      <c r="O84" s="8"/>
+      <c r="O84" s="11"/>
       <c r="P84" s="2"/>
       <c r="Q84" s="2"/>
-      <c r="R84" s="8"/>
+      <c r="R84" s="11"/>
       <c r="S84" s="2"/>
-      <c r="T84" s="2"/>
-    </row>
-    <row r="85" ht="66" spans="1:20">
+      <c r="T84" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="85" ht="66" customHeight="1" spans="1:21">
       <c r="A85" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>22</v>
@@ -8293,37 +8878,37 @@
         <v>82</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K85" s="2"/>
-      <c r="L85" s="8"/>
+      <c r="L85" s="11"/>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
-      <c r="O85" s="8"/>
+      <c r="O85" s="11"/>
       <c r="P85" s="2"/>
       <c r="Q85" s="2"/>
-      <c r="R85" s="8"/>
+      <c r="R85" s="11"/>
       <c r="S85" s="2"/>
       <c r="T85" s="2"/>
     </row>
-    <row r="86" ht="66" spans="1:20">
+    <row r="86" ht="66" customHeight="1" spans="1:21">
       <c r="A86" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>22</v>
@@ -8335,37 +8920,37 @@
         <v>94</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K86" s="2"/>
-      <c r="L86" s="8"/>
+      <c r="L86" s="11"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
-      <c r="O86" s="8"/>
+      <c r="O86" s="11"/>
       <c r="P86" s="2"/>
       <c r="Q86" s="2"/>
-      <c r="R86" s="8"/>
+      <c r="R86" s="11"/>
       <c r="S86" s="2"/>
       <c r="T86" s="2"/>
     </row>
-    <row r="87" ht="33" spans="1:20">
+    <row r="87" ht="33" customHeight="1" spans="1:21">
       <c r="A87" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>22</v>
@@ -8377,37 +8962,37 @@
         <v>107</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K87" s="2"/>
-      <c r="L87" s="8"/>
+      <c r="L87" s="11"/>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
-      <c r="O87" s="8"/>
+      <c r="O87" s="11"/>
       <c r="P87" s="2"/>
       <c r="Q87" s="2"/>
-      <c r="R87" s="8"/>
+      <c r="R87" s="11"/>
       <c r="S87" s="2"/>
       <c r="T87" s="2"/>
     </row>
-    <row r="88" ht="33" spans="1:20">
+    <row r="88" ht="33" customHeight="1" spans="1:21">
       <c r="A88" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>22</v>
@@ -8419,160 +9004,1200 @@
         <v>107</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K88" s="2"/>
-      <c r="L88" s="8"/>
+      <c r="L88" s="11"/>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
-      <c r="O88" s="8"/>
+      <c r="O88" s="11"/>
       <c r="P88" s="2"/>
       <c r="Q88" s="2"/>
-      <c r="R88" s="8"/>
+      <c r="R88" s="11"/>
       <c r="S88" s="2"/>
       <c r="T88" s="2"/>
     </row>
-    <row r="89" ht="66" spans="1:20">
-      <c r="A89" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="B89" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C89" s="9" t="s">
+    <row r="89" ht="66" customHeight="1" spans="1:21">
+      <c r="A89" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C89" s="12" t="s">
         <v>438</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E89" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="F89" s="9" t="s">
+      <c r="E89" s="12" t="s">
         <v>520</v>
       </c>
-      <c r="G89" s="9" t="s">
+      <c r="F89" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="H89" s="9" t="s">
+      <c r="G89" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="I89" s="9" t="s">
+      <c r="H89" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="J89" s="9" t="s">
+      <c r="I89" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="J89" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K89" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M89" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N89" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P89" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q89" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R89" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S89" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T89" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="90" ht="82.5" spans="1:20">
-      <c r="A90" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C90" s="9" t="s">
+      <c r="K89" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L89" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M89" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N89" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O89" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P89" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q89" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R89" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S89" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T89" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="90" ht="82.5" customHeight="1" spans="1:21">
+      <c r="A90" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C90" s="12" t="s">
         <v>438</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E90" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="F90" s="9" t="s">
+      <c r="E90" s="12" t="s">
         <v>526</v>
       </c>
-      <c r="G90" s="9" t="s">
+      <c r="F90" s="12" t="s">
         <v>527</v>
       </c>
-      <c r="H90" s="9" t="s">
+      <c r="G90" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="I90" s="9" t="s">
+      <c r="H90" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="J90" s="9" t="s">
+      <c r="I90" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="J90" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K90" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L90" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M90" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N90" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O90" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P90" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q90" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R90" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S90" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T90" s="9" t="s">
+      <c r="K90" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L90" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M90" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N90" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O90" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P90" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q90" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R90" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S90" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T90" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="91" ht="66" spans="1:21">
+      <c r="A91" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O91" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P91" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q91" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R91" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S91" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U91" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="92" ht="49.5" spans="1:21">
+      <c r="A92" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P92" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q92" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R92" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S92" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T92" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U92" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="93" ht="66" spans="1:21">
+      <c r="A93" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P93" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q93" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R93" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S93" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T93" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U93" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="94" ht="49.5" spans="1:21">
+      <c r="A94" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q94" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R94" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S94" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U94" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="95" ht="66" spans="1:21">
+      <c r="A95" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q95" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R95" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S95" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T95" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U95" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="96" ht="66" spans="1:21">
+      <c r="A96" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P96" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q96" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R96" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S96" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T96" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U96" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="97" ht="66" spans="1:21">
+      <c r="A97" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P97" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q97" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R97" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S97" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T97" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U97" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="98" ht="66" spans="1:21">
+      <c r="A98" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P98" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q98" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R98" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S98" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T98" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U98" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="99" ht="49.5" spans="1:21">
+      <c r="A99" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P99" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q99" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R99" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S99" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T99" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U99" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="100" ht="49.5" spans="1:21">
+      <c r="A100" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P100" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q100" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R100" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S100" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U100" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="101" ht="49.5" spans="1:21">
+      <c r="A101" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M101" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N101" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P101" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q101" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R101" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S101" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U101" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="102" ht="49.5" spans="1:21">
+      <c r="A102" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q102" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R102" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S102" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U102" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="103" ht="33" spans="1:21">
+      <c r="A103" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P103" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q103" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R103" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S103" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T103" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U103" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="104" ht="33" spans="1:21">
+      <c r="A104" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N104" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O104" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P104" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q104" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R104" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S104" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T104" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U104" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="105" ht="49.5" spans="1:21">
+      <c r="A105" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N105" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O105" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P105" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q105" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R105" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S105" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T105" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U105" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="106" ht="66" spans="1:21">
+      <c r="A106" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O106" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P106" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q106" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R106" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S106" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T106" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U106" t="s">
         <v>125</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O90" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O106" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="4">
@@ -8635,7 +10260,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T58"/>
+  <dimension ref="A1:U80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -8721,25 +10346,25 @@
       <c r="A2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
     </row>
     <row r="3" ht="108" customHeight="1" spans="1:20">
       <c r="A3" s="2" t="s">
@@ -8755,31 +10380,31 @@
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>530</v>
+        <v>621</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>531</v>
+        <v>622</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>532</v>
+        <v>623</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>533</v>
+        <v>624</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>534</v>
+        <v>625</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="8"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="11"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-      <c r="O3" s="8"/>
+      <c r="O3" s="11"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
-      <c r="R3" s="8"/>
+      <c r="R3" s="11"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
     </row>
@@ -8797,31 +10422,31 @@
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>535</v>
+        <v>626</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>536</v>
+        <v>627</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>532</v>
+        <v>623</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>537</v>
+        <v>628</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>538</v>
+        <v>629</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="7"/>
-      <c r="L4" s="8"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="11"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
-      <c r="O4" s="8"/>
+      <c r="O4" s="11"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
-      <c r="R4" s="8"/>
+      <c r="R4" s="11"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
     </row>
@@ -8839,31 +10464,31 @@
         <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>539</v>
+        <v>630</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>540</v>
+        <v>631</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>59</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>541</v>
+        <v>632</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>542</v>
+        <v>633</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="8"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="11"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
-      <c r="O5" s="8"/>
+      <c r="O5" s="11"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-      <c r="R5" s="8"/>
+      <c r="R5" s="11"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
     </row>
@@ -8881,31 +10506,31 @@
         <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>543</v>
+        <v>634</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>544</v>
+        <v>635</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>545</v>
+        <v>636</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>546</v>
+        <v>637</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>547</v>
+        <v>638</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K6" s="2"/>
-      <c r="L6" s="8"/>
+      <c r="L6" s="11"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
-      <c r="O6" s="8"/>
+      <c r="O6" s="11"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-      <c r="R6" s="8"/>
+      <c r="R6" s="11"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
     </row>
@@ -8923,31 +10548,31 @@
         <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>548</v>
+        <v>639</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>549</v>
+        <v>640</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>550</v>
+        <v>641</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>551</v>
+        <v>642</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>552</v>
+        <v>643</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K7" s="2"/>
-      <c r="L7" s="8"/>
+      <c r="L7" s="11"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="8"/>
+      <c r="O7" s="11"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
-      <c r="R7" s="8"/>
+      <c r="R7" s="11"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
     </row>
@@ -8965,31 +10590,31 @@
         <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>553</v>
+        <v>644</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>554</v>
+        <v>645</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>555</v>
+        <v>646</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>556</v>
+        <v>647</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>557</v>
+        <v>648</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K8" s="2"/>
-      <c r="L8" s="8"/>
+      <c r="L8" s="11"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="8"/>
+      <c r="O8" s="11"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
-      <c r="R8" s="8"/>
+      <c r="R8" s="11"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
     </row>
@@ -9007,31 +10632,31 @@
         <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>558</v>
+        <v>649</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>559</v>
+        <v>650</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>560</v>
+        <v>651</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>561</v>
+        <v>652</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>562</v>
+        <v>653</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K9" s="2"/>
-      <c r="L9" s="8"/>
+      <c r="L9" s="11"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="8"/>
+      <c r="O9" s="11"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
-      <c r="R9" s="8"/>
+      <c r="R9" s="11"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
     </row>
@@ -9049,31 +10674,31 @@
         <v>82</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>563</v>
+        <v>654</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>564</v>
+        <v>655</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>532</v>
+        <v>623</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>565</v>
+        <v>656</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>566</v>
+        <v>657</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K10" s="2"/>
-      <c r="L10" s="8"/>
+      <c r="L10" s="11"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="8"/>
+      <c r="O10" s="11"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
-      <c r="R10" s="8"/>
+      <c r="R10" s="11"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
     </row>
@@ -9091,31 +10716,31 @@
         <v>82</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>567</v>
+        <v>658</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>568</v>
+        <v>659</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>532</v>
+        <v>623</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>569</v>
+        <v>660</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>570</v>
+        <v>661</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K11" s="2"/>
-      <c r="L11" s="8"/>
+      <c r="L11" s="11"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="8"/>
+      <c r="O11" s="11"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
-      <c r="R11" s="8"/>
+      <c r="R11" s="11"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
@@ -9133,31 +10758,31 @@
         <v>94</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>571</v>
+        <v>662</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>572</v>
+        <v>663</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>573</v>
+        <v>664</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>574</v>
+        <v>665</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>575</v>
+        <v>666</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K12" s="2"/>
-      <c r="L12" s="8"/>
+      <c r="L12" s="11"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="8"/>
+      <c r="O12" s="11"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
-      <c r="R12" s="8"/>
+      <c r="R12" s="11"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
@@ -9175,31 +10800,31 @@
         <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>576</v>
+        <v>667</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>577</v>
+        <v>668</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>578</v>
+        <v>669</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>579</v>
+        <v>670</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>580</v>
+        <v>671</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K13" s="2"/>
-      <c r="L13" s="8"/>
+      <c r="L13" s="11"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="8"/>
+      <c r="O13" s="11"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-      <c r="R13" s="8"/>
+      <c r="R13" s="11"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
@@ -9217,217 +10842,217 @@
         <v>107</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>581</v>
+        <v>672</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>582</v>
+        <v>673</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>545</v>
+        <v>636</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>583</v>
+        <v>674</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>584</v>
+        <v>675</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K14" s="2"/>
-      <c r="L14" s="8"/>
+      <c r="L14" s="11"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
-      <c r="O14" s="8"/>
+      <c r="O14" s="11"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
-      <c r="R14" s="8"/>
+      <c r="R14" s="11"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:20">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="B15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="J15" s="9" t="s">
+      <c r="F15" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>678</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="J15" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T15" s="9" t="s">
+      <c r="K15" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M15" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R15" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S15" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T15" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="16" ht="72" customHeight="1" spans="1:20">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>589</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>590</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>591</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>592</v>
-      </c>
-      <c r="J16" s="9" t="s">
+      <c r="E16" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>681</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="J16" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R16" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S16" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T16" s="9" t="s">
+      <c r="K16" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R16" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S16" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T16" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="17" ht="54" customHeight="1" spans="1:20">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="B17" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="G17" s="9" t="s">
-        <v>593</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>594</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>595</v>
-      </c>
-      <c r="J17" s="9" t="s">
+      <c r="G17" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>685</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>686</v>
+      </c>
+      <c r="J17" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T17" s="9" t="s">
+      <c r="K17" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q17" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R17" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S17" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T17" s="12" t="s">
         <v>125</v>
       </c>
     </row>
@@ -9448,16 +11073,16 @@
         <v>145</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>596</v>
+        <v>687</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>532</v>
+        <v>623</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>597</v>
+        <v>688</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>598</v>
+        <v>689</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>37</v>
@@ -9510,16 +11135,16 @@
         <v>150</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>599</v>
+        <v>690</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>586</v>
+        <v>677</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>600</v>
+        <v>691</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>601</v>
+        <v>692</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>37</v>
@@ -9569,19 +11194,19 @@
         <v>24</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>602</v>
+        <v>693</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>603</v>
+        <v>694</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>604</v>
+        <v>695</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>605</v>
+        <v>696</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>37</v>
@@ -9631,19 +11256,19 @@
         <v>24</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>606</v>
+        <v>697</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>607</v>
+        <v>698</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>586</v>
+        <v>677</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>608</v>
+        <v>699</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>609</v>
+        <v>700</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>37</v>
@@ -9696,16 +11321,16 @@
         <v>173</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>610</v>
+        <v>701</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>611</v>
+        <v>702</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>612</v>
+        <v>703</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>613</v>
+        <v>704</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>37</v>
@@ -9755,19 +11380,19 @@
         <v>24</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>614</v>
+        <v>705</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>615</v>
+        <v>706</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>616</v>
+        <v>707</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>617</v>
+        <v>708</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>618</v>
+        <v>709</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>37</v>
@@ -9817,19 +11442,19 @@
         <v>24</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>619</v>
+        <v>710</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>620</v>
+        <v>711</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>621</v>
+        <v>712</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>617</v>
+        <v>708</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>622</v>
+        <v>713</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>37</v>
@@ -9879,19 +11504,19 @@
         <v>24</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>623</v>
+        <v>714</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>624</v>
+        <v>715</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>625</v>
+        <v>716</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>617</v>
+        <v>708</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>626</v>
+        <v>717</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>37</v>
@@ -9941,19 +11566,19 @@
         <v>24</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>627</v>
+        <v>718</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>628</v>
+        <v>719</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>629</v>
+        <v>720</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>630</v>
+        <v>721</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>631</v>
+        <v>722</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>37</v>
@@ -10003,19 +11628,19 @@
         <v>24</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>632</v>
+        <v>723</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>633</v>
+        <v>724</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>545</v>
+        <v>636</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>634</v>
+        <v>725</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>635</v>
+        <v>726</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>74</v>
@@ -10065,19 +11690,19 @@
         <v>24</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>636</v>
+        <v>727</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>637</v>
+        <v>728</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>638</v>
+        <v>729</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>639</v>
+        <v>730</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>640</v>
+        <v>731</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>37</v>
@@ -10117,25 +11742,25 @@
       <c r="A29" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:20">
       <c r="A30" s="2" t="s">
@@ -10160,22 +11785,22 @@
         <v>252</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>641</v>
+        <v>732</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>642</v>
+        <v>733</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K30" s="2"/>
-      <c r="L30" s="8"/>
+      <c r="L30" s="11"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
-      <c r="O30" s="8"/>
+      <c r="O30" s="11"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
-      <c r="R30" s="8"/>
+      <c r="R30" s="11"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
     </row>
@@ -10193,31 +11818,31 @@
         <v>24</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>643</v>
+        <v>734</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>644</v>
+        <v>735</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>116</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>645</v>
+        <v>736</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>646</v>
+        <v>737</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K31" s="2"/>
-      <c r="L31" s="8"/>
+      <c r="L31" s="11"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
-      <c r="O31" s="8"/>
+      <c r="O31" s="11"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
-      <c r="R31" s="8"/>
+      <c r="R31" s="11"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
     </row>
@@ -10235,31 +11860,31 @@
         <v>24</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>647</v>
+        <v>738</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>648</v>
+        <v>739</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>649</v>
+        <v>740</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>650</v>
+        <v>741</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>651</v>
+        <v>742</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K32" s="2"/>
-      <c r="L32" s="8"/>
+      <c r="L32" s="11"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
-      <c r="O32" s="8"/>
+      <c r="O32" s="11"/>
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
-      <c r="R32" s="8"/>
+      <c r="R32" s="11"/>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
     </row>
@@ -10277,31 +11902,31 @@
         <v>24</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>652</v>
+        <v>743</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>653</v>
+        <v>744</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>116</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>654</v>
+        <v>745</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>655</v>
+        <v>746</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="8"/>
+      <c r="L33" s="11"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
-      <c r="O33" s="8"/>
+      <c r="O33" s="11"/>
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
-      <c r="R33" s="8"/>
+      <c r="R33" s="11"/>
       <c r="S33" s="2"/>
       <c r="T33" s="2"/>
     </row>
@@ -10322,28 +11947,28 @@
         <v>272</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>656</v>
+        <v>747</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>657</v>
+        <v>748</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>658</v>
+        <v>749</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>659</v>
+        <v>750</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K34" s="2"/>
-      <c r="L34" s="8"/>
+      <c r="L34" s="11"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
-      <c r="O34" s="8"/>
+      <c r="O34" s="11"/>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
-      <c r="R34" s="8"/>
+      <c r="R34" s="11"/>
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
     </row>
@@ -10361,31 +11986,31 @@
         <v>24</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>660</v>
+        <v>751</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>279</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>661</v>
+        <v>752</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>662</v>
+        <v>753</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>663</v>
+        <v>754</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K35" s="2"/>
-      <c r="L35" s="8"/>
+      <c r="L35" s="11"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
-      <c r="O35" s="8"/>
+      <c r="O35" s="11"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
-      <c r="R35" s="8"/>
+      <c r="R35" s="11"/>
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
     </row>
@@ -10403,31 +12028,31 @@
         <v>24</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>664</v>
+        <v>755</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>665</v>
+        <v>756</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>116</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>666</v>
+        <v>757</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>667</v>
+        <v>758</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K36" s="2"/>
-      <c r="L36" s="8"/>
+      <c r="L36" s="11"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
-      <c r="O36" s="8"/>
+      <c r="O36" s="11"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
-      <c r="R36" s="8"/>
+      <c r="R36" s="11"/>
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
     </row>
@@ -10445,31 +12070,31 @@
         <v>24</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>668</v>
+        <v>759</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>669</v>
+        <v>760</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>670</v>
+        <v>761</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>671</v>
+        <v>762</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>672</v>
+        <v>763</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K37" s="2"/>
-      <c r="L37" s="8"/>
+      <c r="L37" s="11"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
-      <c r="O37" s="8"/>
+      <c r="O37" s="11"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
-      <c r="R37" s="8"/>
+      <c r="R37" s="11"/>
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
     </row>
@@ -10487,31 +12112,31 @@
         <v>24</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>673</v>
+        <v>764</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>674</v>
+        <v>765</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>297</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>675</v>
+        <v>766</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>676</v>
+        <v>767</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K38" s="2"/>
-      <c r="L38" s="8"/>
+      <c r="L38" s="11"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
-      <c r="O38" s="8"/>
+      <c r="O38" s="11"/>
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
-      <c r="R38" s="8"/>
+      <c r="R38" s="11"/>
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
     </row>
@@ -10529,31 +12154,31 @@
         <v>82</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>677</v>
+        <v>768</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>678</v>
+        <v>769</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>303</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>679</v>
+        <v>770</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>680</v>
+        <v>771</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K39" s="2"/>
-      <c r="L39" s="8"/>
+      <c r="L39" s="11"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
-      <c r="O39" s="8"/>
+      <c r="O39" s="11"/>
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
-      <c r="R39" s="8"/>
+      <c r="R39" s="11"/>
       <c r="S39" s="2"/>
       <c r="T39" s="2"/>
     </row>
@@ -10571,31 +12196,31 @@
         <v>94</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>681</v>
+        <v>772</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>682</v>
+        <v>773</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>683</v>
+        <v>774</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>684</v>
+        <v>775</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>685</v>
+        <v>776</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K40" s="2"/>
-      <c r="L40" s="8"/>
+      <c r="L40" s="11"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
-      <c r="O40" s="8"/>
+      <c r="O40" s="11"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
-      <c r="R40" s="8"/>
+      <c r="R40" s="11"/>
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
     </row>
@@ -10616,214 +12241,214 @@
         <v>319</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>686</v>
+        <v>777</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>116</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>687</v>
+        <v>778</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>688</v>
+        <v>779</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K41" s="2"/>
-      <c r="L41" s="8"/>
+      <c r="L41" s="11"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
-      <c r="O41" s="8"/>
+      <c r="O41" s="11"/>
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
-      <c r="R41" s="8"/>
+      <c r="R41" s="11"/>
       <c r="S41" s="2"/>
       <c r="T41" s="2"/>
     </row>
     <row r="42" ht="33" customHeight="1" spans="1:20">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="B42" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" s="9" t="s">
+      <c r="B42" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="12" t="s">
         <v>247</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E42" s="9" t="s">
-        <v>689</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="G42" s="9" t="s">
+      <c r="E42" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>781</v>
+      </c>
+      <c r="G42" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="H42" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>692</v>
-      </c>
-      <c r="J42" s="9" t="s">
+      <c r="H42" s="12" t="s">
+        <v>782</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>783</v>
+      </c>
+      <c r="J42" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K42" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L42" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M42" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N42" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O42" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P42" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q42" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R42" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S42" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T42" s="9" t="s">
+      <c r="K42" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L42" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M42" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O42" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P42" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q42" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R42" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S42" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T42" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="43" ht="33" customHeight="1" spans="1:20">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="9" t="s">
+      <c r="B43" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="12" t="s">
         <v>247</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="G43" s="9" t="s">
+      <c r="F43" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="G43" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="H43" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>695</v>
-      </c>
-      <c r="J43" s="9" t="s">
+      <c r="H43" s="12" t="s">
+        <v>785</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>786</v>
+      </c>
+      <c r="J43" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K43" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M43" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N43" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P43" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q43" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R43" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S43" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T43" s="9" t="s">
+      <c r="K43" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L43" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O43" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P43" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q43" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R43" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S43" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T43" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="44" ht="33" customHeight="1" spans="1:20">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" s="9" t="s">
+      <c r="B44" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="12" t="s">
         <v>247</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F44" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="H44" s="9" t="s">
-        <v>696</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>697</v>
-      </c>
-      <c r="J44" s="9" t="s">
+      <c r="H44" s="12" t="s">
+        <v>787</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>788</v>
+      </c>
+      <c r="J44" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K44" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L44" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M44" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N44" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O44" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P44" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q44" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R44" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S44" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T44" s="9" t="s">
+      <c r="K44" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L44" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M44" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O44" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P44" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q44" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R44" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S44" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T44" s="12" t="s">
         <v>125</v>
       </c>
     </row>
@@ -10831,25 +12456,25 @@
       <c r="A45" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="6"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="8"/>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="8"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
     </row>
     <row r="46" ht="49.5" customHeight="1" spans="1:20">
       <c r="A46" s="2" t="s">
@@ -10865,31 +12490,31 @@
         <v>24</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>698</v>
+        <v>789</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>699</v>
+        <v>790</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>700</v>
+        <v>791</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>701</v>
+        <v>792</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>702</v>
+        <v>793</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K46" s="2"/>
-      <c r="L46" s="8"/>
+      <c r="L46" s="11"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
-      <c r="O46" s="8"/>
+      <c r="O46" s="11"/>
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
-      <c r="R46" s="8"/>
+      <c r="R46" s="11"/>
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
     </row>
@@ -10907,35 +12532,35 @@
         <v>24</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>703</v>
+        <v>794</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>703</v>
+        <v>794</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>704</v>
+        <v>795</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>705</v>
+        <v>796</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>706</v>
+        <v>797</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K47" s="2"/>
-      <c r="L47" s="8"/>
+      <c r="L47" s="11"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
-      <c r="O47" s="8"/>
+      <c r="O47" s="11"/>
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
-      <c r="R47" s="8"/>
+      <c r="R47" s="11"/>
       <c r="S47" s="2"/>
       <c r="T47" s="2"/>
     </row>
-    <row r="48" ht="49.5" spans="1:20">
+    <row r="48" ht="49.5" customHeight="1" spans="1:20">
       <c r="A48" s="2" t="s">
         <v>282</v>
       </c>
@@ -10949,35 +12574,35 @@
         <v>24</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>707</v>
+        <v>798</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>707</v>
+        <v>798</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>708</v>
+        <v>799</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>709</v>
+        <v>800</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>710</v>
+        <v>801</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K48" s="2"/>
-      <c r="L48" s="8"/>
+      <c r="L48" s="11"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="8"/>
+      <c r="O48" s="11"/>
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
-      <c r="R48" s="8"/>
+      <c r="R48" s="11"/>
       <c r="S48" s="2"/>
       <c r="T48" s="2"/>
     </row>
-    <row r="49" ht="49.5" spans="1:20">
+    <row r="49" ht="49.5" customHeight="1" spans="1:21">
       <c r="A49" s="2" t="s">
         <v>288</v>
       </c>
@@ -10991,35 +12616,35 @@
         <v>24</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>711</v>
+        <v>802</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>712</v>
+        <v>803</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>704</v>
+        <v>795</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>713</v>
+        <v>804</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>714</v>
+        <v>805</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K49" s="2"/>
-      <c r="L49" s="8"/>
+      <c r="L49" s="11"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-      <c r="O49" s="8"/>
+      <c r="O49" s="11"/>
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
-      <c r="R49" s="8"/>
+      <c r="R49" s="11"/>
       <c r="S49" s="2"/>
       <c r="T49" s="2"/>
     </row>
-    <row r="50" ht="49.5" spans="1:20">
+    <row r="50" ht="49.5" customHeight="1" spans="1:21">
       <c r="A50" s="2" t="s">
         <v>294</v>
       </c>
@@ -11033,35 +12658,35 @@
         <v>24</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>715</v>
+        <v>806</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>716</v>
+        <v>807</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>704</v>
+        <v>795</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>717</v>
+        <v>808</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>718</v>
+        <v>809</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K50" s="2"/>
-      <c r="L50" s="8"/>
+      <c r="L50" s="11"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
-      <c r="O50" s="8"/>
+      <c r="O50" s="11"/>
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
-      <c r="R50" s="8"/>
+      <c r="R50" s="11"/>
       <c r="S50" s="2"/>
       <c r="T50" s="2"/>
     </row>
-    <row r="51" ht="49.5" spans="1:20">
+    <row r="51" ht="49.5" customHeight="1" spans="1:21">
       <c r="A51" s="2" t="s">
         <v>300</v>
       </c>
@@ -11075,35 +12700,35 @@
         <v>24</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>719</v>
+        <v>810</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>720</v>
+        <v>811</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>116</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>721</v>
+        <v>812</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>722</v>
+        <v>813</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K51" s="2"/>
-      <c r="L51" s="8"/>
+      <c r="L51" s="11"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="8"/>
+      <c r="O51" s="11"/>
       <c r="P51" s="2"/>
       <c r="Q51" s="2"/>
-      <c r="R51" s="8"/>
+      <c r="R51" s="11"/>
       <c r="S51" s="2"/>
       <c r="T51" s="2"/>
     </row>
-    <row r="52" ht="49.5" spans="1:20">
+    <row r="52" ht="49.5" customHeight="1" spans="1:21">
       <c r="A52" s="2" t="s">
         <v>306</v>
       </c>
@@ -11120,32 +12745,32 @@
         <v>395</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>723</v>
+        <v>814</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>116</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>724</v>
+        <v>815</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>725</v>
+        <v>816</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K52" s="2"/>
-      <c r="L52" s="8"/>
+      <c r="L52" s="11"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="8"/>
+      <c r="O52" s="11"/>
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
-      <c r="R52" s="8"/>
+      <c r="R52" s="11"/>
       <c r="S52" s="2"/>
       <c r="T52" s="2"/>
     </row>
-    <row r="53" ht="33" spans="1:20">
+    <row r="53" ht="33" customHeight="1" spans="1:21">
       <c r="A53" s="2" t="s">
         <v>312</v>
       </c>
@@ -11162,32 +12787,32 @@
         <v>400</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>726</v>
+        <v>817</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>727</v>
+        <v>818</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>728</v>
+        <v>819</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>729</v>
+        <v>820</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K53" s="2"/>
-      <c r="L53" s="8"/>
+      <c r="L53" s="11"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
-      <c r="O53" s="8"/>
+      <c r="O53" s="11"/>
       <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
-      <c r="R53" s="8"/>
+      <c r="R53" s="11"/>
       <c r="S53" s="2"/>
       <c r="T53" s="2"/>
     </row>
-    <row r="54" ht="33" spans="1:20">
+    <row r="54" ht="33" customHeight="1" spans="1:21">
       <c r="A54" s="2" t="s">
         <v>318</v>
       </c>
@@ -11201,35 +12826,35 @@
         <v>94</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>730</v>
+        <v>821</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>731</v>
+        <v>822</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>732</v>
+        <v>823</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>733</v>
+        <v>824</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>734</v>
+        <v>825</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K54" s="2"/>
-      <c r="L54" s="8"/>
+      <c r="L54" s="11"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
-      <c r="O54" s="8"/>
+      <c r="O54" s="11"/>
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
-      <c r="R54" s="8"/>
+      <c r="R54" s="11"/>
       <c r="S54" s="2"/>
       <c r="T54" s="2"/>
     </row>
-    <row r="55" ht="33" spans="1:20">
+    <row r="55" ht="33" customHeight="1" spans="1:21">
       <c r="A55" s="2" t="s">
         <v>323</v>
       </c>
@@ -11246,222 +12871,1593 @@
         <v>418</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>735</v>
+        <v>826</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>736</v>
+        <v>827</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>737</v>
+        <v>828</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>738</v>
+        <v>829</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K55" s="2"/>
-      <c r="L55" s="8"/>
+      <c r="L55" s="11"/>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
-      <c r="O55" s="8"/>
+      <c r="O55" s="11"/>
       <c r="P55" s="2"/>
       <c r="Q55" s="2"/>
-      <c r="R55" s="8"/>
+      <c r="R55" s="11"/>
       <c r="S55" s="2"/>
       <c r="T55" s="2"/>
     </row>
-    <row r="56" ht="49.5" spans="1:20">
-      <c r="A56" s="9" t="s">
+    <row r="56" ht="49.5" customHeight="1" spans="1:21">
+      <c r="A56" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B56" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C56" s="9" t="s">
+      <c r="B56" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="12" t="s">
         <v>345</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" s="12" t="s">
         <v>434</v>
       </c>
-      <c r="F56" s="9" t="s">
-        <v>739</v>
-      </c>
-      <c r="G56" s="9" t="s">
+      <c r="F56" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="G56" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="H56" s="9" t="s">
-        <v>740</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>741</v>
-      </c>
-      <c r="J56" s="9" t="s">
+      <c r="H56" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>832</v>
+      </c>
+      <c r="J56" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S56" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T56" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="57" ht="49.5" spans="1:20">
-      <c r="A57" s="9" t="s">
+      <c r="K56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S56" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T56" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57" ht="49.5" customHeight="1" spans="1:21">
+      <c r="A57" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="B57" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C57" s="9" t="s">
+      <c r="B57" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="12" t="s">
         <v>345</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>742</v>
-      </c>
-      <c r="G57" s="9" t="s">
+      <c r="F57" s="12" t="s">
+        <v>833</v>
+      </c>
+      <c r="G57" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="H57" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>744</v>
-      </c>
-      <c r="J57" s="9" t="s">
+      <c r="H57" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>835</v>
+      </c>
+      <c r="J57" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T57" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="58" ht="33" spans="1:20">
-      <c r="A58" s="9" t="s">
+      <c r="K57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S57" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T57" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" ht="33" customHeight="1" spans="1:21">
+      <c r="A58" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="B58" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C58" s="9" t="s">
+      <c r="B58" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58" s="12" t="s">
         <v>345</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="F58" s="9" t="s">
-        <v>745</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>746</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>747</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="J58" s="9" t="s">
+      <c r="F58" s="12" t="s">
+        <v>836</v>
+      </c>
+      <c r="G58" s="12" t="s">
+        <v>837</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="J58" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K58" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L58" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M58" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N58" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O58" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P58" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q58" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R58" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="S58" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="T58" s="9" t="s">
+      <c r="K58" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="L58" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M58" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N58" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="O58" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P58" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q58" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="R58" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="S58" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T58" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:21">
+      <c r="A59" s="13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="60" ht="49.5" spans="1:21">
+      <c r="A60" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U60" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="61" ht="66" spans="1:21">
+      <c r="A61" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T61" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U61" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="62" ht="66" spans="1:21">
+      <c r="A62" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U62" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" ht="66" spans="1:21">
+      <c r="A63" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T63" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" ht="49.5" spans="1:21">
+      <c r="A64" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T64" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U64" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" ht="66" spans="1:21">
+      <c r="A65" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R65" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T65" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U65" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" ht="66" spans="1:21">
+      <c r="A66" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U66" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="67" ht="49.5" spans="1:21">
+      <c r="A67" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q67" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R67" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S67" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T67" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U67" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="68" ht="66" spans="1:21">
+      <c r="A68" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q68" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R68" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T68" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U68" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="69" ht="49.5" spans="1:21">
+      <c r="A69" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T69" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U69" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="70" ht="66" spans="1:21">
+      <c r="A70" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T70" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U70" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="71" ht="66" spans="1:21">
+      <c r="A71" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q71" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R71" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S71" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T71" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U71" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="72" ht="66" spans="1:21">
+      <c r="A72" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U72" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="73" ht="49.5" spans="1:21">
+      <c r="A73" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q73" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R73" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T73" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U73" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="74" ht="49.5" spans="1:21">
+      <c r="A74" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q74" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R74" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T74" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U74" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="75" ht="66" spans="1:21">
+      <c r="A75" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q75" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R75" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T75" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U75" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="76" ht="33" spans="1:21">
+      <c r="A76" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q76" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R76" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S76" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U76" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="77" ht="33" spans="1:21">
+      <c r="A77" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q77" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R77" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S77" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T77" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U77" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="78" ht="33" spans="1:21">
+      <c r="A78" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q78" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R78" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S78" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T78" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U78" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="79" ht="49.5" spans="1:21">
+      <c r="A79" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q79" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R79" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T79" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U79" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="80" ht="66" spans="1:21">
+      <c r="A80" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T80" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="U80" t="s">
         <v>125</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A59:J59"/>
   </mergeCells>
   <conditionalFormatting sqref="K2:K10000">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
@@ -11592,31 +14588,31 @@
     </row>
     <row r="2" ht="198" customHeight="1" spans="1:20">
       <c r="A2" s="2" t="s">
-        <v>749</v>
+        <v>888</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>750</v>
+        <v>889</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>751</v>
+        <v>890</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>752</v>
+        <v>891</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>753</v>
+        <v>892</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>754</v>
+        <v>893</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>755</v>
+        <v>894</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>30</v>
@@ -11634,31 +14630,31 @@
     </row>
     <row r="3" ht="198" customHeight="1" spans="1:20">
       <c r="A3" s="2" t="s">
-        <v>756</v>
+        <v>895</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>750</v>
+        <v>889</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>757</v>
+        <v>896</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>758</v>
+        <v>897</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>759</v>
+        <v>898</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>760</v>
+        <v>899</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>761</v>
+        <v>900</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>30</v>
@@ -11676,31 +14672,31 @@
     </row>
     <row r="4" ht="180" customHeight="1" spans="1:20">
       <c r="A4" s="2" t="s">
-        <v>762</v>
+        <v>901</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>750</v>
+        <v>889</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>763</v>
+        <v>902</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>764</v>
+        <v>903</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>765</v>
+        <v>904</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>766</v>
+        <v>905</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>767</v>
+        <v>906</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>30</v>
@@ -11718,31 +14714,31 @@
     </row>
     <row r="5" ht="144" customHeight="1" spans="1:20">
       <c r="A5" s="2" t="s">
-        <v>768</v>
+        <v>907</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>750</v>
+        <v>889</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>769</v>
+        <v>908</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>770</v>
+        <v>909</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>252</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>771</v>
+        <v>910</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>772</v>
+        <v>911</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>30</v>
@@ -11760,31 +14756,31 @@
     </row>
     <row r="6" ht="162" customHeight="1" spans="1:20">
       <c r="A6" s="2" t="s">
-        <v>773</v>
+        <v>912</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>750</v>
+        <v>889</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>774</v>
+        <v>913</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>775</v>
+        <v>914</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>776</v>
+        <v>915</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>777</v>
+        <v>916</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>778</v>
+        <v>917</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>30</v>
@@ -11802,31 +14798,31 @@
     </row>
     <row r="7" ht="144" customHeight="1" spans="1:20">
       <c r="A7" s="2" t="s">
-        <v>779</v>
+        <v>918</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>750</v>
+        <v>889</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>780</v>
+        <v>919</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>781</v>
+        <v>920</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>782</v>
+        <v>921</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>783</v>
+        <v>922</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>784</v>
+        <v>923</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>30</v>
